--- a/data/trans_dic/IP16A12_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A12_2023-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido medicamentos para bajar la fiebre</t>
+          <t>Menores que han  consumido medicamentos para bajar la fiebre (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,79; 39,73</t>
+          <t>9,84; 39,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,33; 45,75</t>
+          <t>17,9; 47,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,27; 39,38</t>
+          <t>18,79; 38,33</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,56; 33,35</t>
+          <t>12,61; 33,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,57; 34,36</t>
+          <t>14,36; 36,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,95; 30,41</t>
+          <t>15,55; 30,5</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,82; 29,5</t>
+          <t>7,97; 29,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,46; 27,1</t>
+          <t>8,33; 29,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,07; 24,78</t>
+          <t>9,91; 24,7</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 15,92</t>
+          <t>1,45; 15,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,03; 26,34</t>
+          <t>10,14; 26,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,09; 17,39</t>
+          <t>5,63; 17,74</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,61; 19,76</t>
+          <t>8,19; 19,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,64; 25,6</t>
+          <t>15,52; 25,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,8; 20,97</t>
+          <t>12,83; 20,93</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han  consumido medicamentos para bajar la fiebre (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3698</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6928</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10626</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1612; 6417</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4002; 10564</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7281; 14852</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>10148</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11209</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>21357</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>5878; 15636</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>7036; 17709</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>14865; 29165</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>6595</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7452</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>14047</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2961; 11017</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3846; 13463</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>8260; 20579</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>5228</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>11147</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>16375</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1147; 11968</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>6609; 17105</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>8131; 25611</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>25669</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>36735</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>62404</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>14685; 35344</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>28349; 47133</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>46438; 75764</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A12_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A12_2023-Edad-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,84; 39,15</t>
+          <t>10,44; 39,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,9; 47,25</t>
+          <t>18,98; 47,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,79; 38,33</t>
+          <t>18,96; 38,66</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,61; 33,54</t>
+          <t>12,68; 33,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,36; 36,15</t>
+          <t>14,22; 35,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,55; 30,5</t>
+          <t>15,82; 30,78</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,97; 29,66</t>
+          <t>9,41; 29,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,33; 29,16</t>
+          <t>7,82; 29,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,91; 24,7</t>
+          <t>10,45; 24,63</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,45; 15,11</t>
+          <t>1,0; 14,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,14; 26,24</t>
+          <t>10,01; 27,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,63; 17,74</t>
+          <t>5,91; 17,95</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,19; 19,71</t>
+          <t>8,51; 19,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,52; 25,8</t>
+          <t>15,04; 25,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,83; 20,93</t>
+          <t>12,46; 20,86</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1612; 6417</t>
+          <t>1711; 6524</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4002; 10564</t>
+          <t>4243; 10671</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7281; 14852</t>
+          <t>7345; 14980</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5878; 15636</t>
+          <t>5912; 15636</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7036; 17709</t>
+          <t>6967; 17189</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14865; 29165</t>
+          <t>15128; 29428</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2961; 11017</t>
+          <t>3497; 10949</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3846; 13463</t>
+          <t>3612; 13702</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8260; 20579</t>
+          <t>8706; 20525</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1147; 11968</t>
+          <t>795; 11802</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6609; 17105</t>
+          <t>6524; 17751</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8131; 25611</t>
+          <t>8533; 25913</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14685; 35344</t>
+          <t>15258; 35624</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>28349; 47133</t>
+          <t>27471; 46478</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>46438; 75764</t>
+          <t>45122; 75508</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A12_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A12_2023-Edad-trans_dic.xlsx
@@ -490,18 +490,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido medicamentos para bajar la fiebre (tasa de respuesta: 100,0%)</t>
+          <t>Menores que consumieron medicamentos para bajar la fiebre (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,1%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,44; 39,8</t>
+          <t>18,56; 45,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,98; 47,73</t>
+          <t>9,64; 39,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,96; 38,66</t>
+          <t>18,37; 38,94</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,42%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,68; 33,54</t>
+          <t>15,22; 36,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,22; 35,09</t>
+          <t>12,31; 31,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,82; 30,78</t>
+          <t>16,33; 31,02</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,16%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,41; 29,47</t>
+          <t>7,7; 27,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,82; 29,68</t>
+          <t>8,09; 30,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,45; 24,63</t>
+          <t>10,3; 25,55</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>14,36%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 14,9</t>
+          <t>9,39; 27,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,01; 27,23</t>
+          <t>4,54; 22,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,91; 17,95</t>
+          <t>9,22; 21,19</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>18,54%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,51; 19,86</t>
+          <t>15,48; 25,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,04; 25,44</t>
+          <t>12,06; 21,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,46; 20,86</t>
+          <t>15,24; 22,41</t>
         </is>
       </c>
     </row>
@@ -825,18 +825,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido medicamentos para bajar la fiebre (tasa de respuesta: 100,0%)</t>
+          <t>Menores que consumieron medicamentos para bajar la fiebre (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3698</t>
+          <t>5397</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6928</t>
+          <t>3249</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10626</t>
+          <t>8646</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1711; 6524</t>
+          <t>3236; 7905</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4243; 10671</t>
+          <t>1395; 5687</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7345; 14980</t>
+          <t>5862; 12424</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>10148</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11209</t>
+          <t>8460</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21357</t>
+          <t>18411</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5912; 15636</t>
+          <t>6276; 14949</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6967; 17189</t>
+          <t>5035; 12684</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15128; 29428</t>
+          <t>13411; 25473</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6595</t>
+          <t>7255</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7452</t>
+          <t>6798</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14047</t>
+          <t>14054</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3497; 10949</t>
+          <t>3387; 12294</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3612; 13702</t>
+          <t>3070; 11392</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8706; 20525</t>
+          <t>8439; 20931</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>5228</t>
+          <t>10948</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11147</t>
+          <t>5451</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16375</t>
+          <t>16399</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>795; 11802</t>
+          <t>5900; 16978</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6524; 17751</t>
+          <t>2329; 11516</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8533; 25913</t>
+          <t>10527; 24192</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>43</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>25669</t>
+          <t>33552</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>36735</t>
+          <t>23957</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>62404</t>
+          <t>57510</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>15258; 35624</t>
+          <t>25608; 42931</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>27471; 46478</t>
+          <t>17446; 31555</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45122; 75508</t>
+          <t>47256; 69490</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A12_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A12_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que consumieron medicamentos para bajar la fiebre (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>30,96%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>22,44%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>27,1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>18,56; 45,34</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>9,64; 39,28</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>18,37; 38,94</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>24,13%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>20,69%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>22,42%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>15,22; 36,25</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>12,31; 31,02</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>16,33; 31,02</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>16,5%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>17,91%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>17,16%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>7,7; 27,96</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>8,09; 30,02</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>10,3; 25,55</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>17,42%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>10,62%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>14,36%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>9,39; 27,02</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>4,54; 22,44</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>9,22; 21,19</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>20,28%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>16,56%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>18,54%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>15,48; 25,94</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>12,06; 21,82</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>15,24; 22,41</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.3096056914768013</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.2244047672819648</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.2709509203981966</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>5397</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>3249</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8646</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.1856091420367506</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.09635319539023322</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.1837129421001777</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>3236; 7905</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1395; 5687</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5862; 12424</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.4534339494406474</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.3928104083728869</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.3893500350903722</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.2413406245437664</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.206856301008555</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.2241696445854683</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>9952</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>8460</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>18411</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.1522041625403446</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.1231172313571345</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.1632839651985503</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>6276; 14949</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>5035; 12684</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>13411; 25473</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.3625391818121123</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.3101511226330088</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.3101561831680387</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.1650030923949767</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.1791456547873818</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.1715544321507194</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>7255</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>6798</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>14054</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.07703276198915029</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.08090725191711425</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.1030167893179174</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>3387; 12294</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>3070; 11392</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>8439; 20931</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.2796030875482456</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.3001976200103921</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.2555088672416093</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.1742211836571655</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.1062116908139626</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.1436478475927621</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>10948</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>5451</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>16399</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.09389354040020738</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.04538031197886186</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.09221382469577627</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>5900; 16978</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>2329; 11516</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>10527; 24192</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.2701747601365535</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.2244013234083767</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.2119135477352413</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.2027592191367933</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.1656328339326856</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.1854433406752149</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>33552</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>23957</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>57510</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.154751667581097</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.1206174450301799</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.1523784629989432</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>25608; 42931</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>17446; 31555</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>47256; 69490</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.2594339984204225</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.2181589745941018</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.2240737278983316</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumieron medicamentos para bajar la fiebre (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>5397</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>3249</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>8646</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>3236</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>1395</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>5862</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>7905</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>5687</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>12424</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>9952</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>8460</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>18411</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>6276</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>5035</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>13411</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>14949</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>12684</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>25473</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>7255</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>6798</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>14054</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>3387</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>3070</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>8439</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>12294</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>11392</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>20931</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>10948</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>5451</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>16399</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>5900</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>2329</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>10527</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>16978</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>11516</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>24192</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>33552</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>23957</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>57510</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>25608</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>17446</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>47256</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>42931</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>31555</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>69490</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>